--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEW_YORK_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEW_YORK_2022.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C208">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C657">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C664">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C749">
